--- a/content/post/drafts/season-prediction/men_predictions.xlsx
+++ b/content/post/drafts/season-prediction/men_predictions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -20,16 +20,10 @@
     <t xml:space="preserve">Nation</t>
   </si>
   <si>
-    <t xml:space="preserve">Pct_of_Max_Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predicted_Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI_Lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI_Upper</t>
+    <t xml:space="preserve">2023-24 Points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-25 Predicted Points</t>
   </si>
   <si>
     <t xml:space="preserve">Johannes Høsflot Klæbo</t>
@@ -41,60 +35,30 @@
     <t xml:space="preserve">0.815204884735367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.753189545244327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.877220224226407</t>
-  </si>
-  <si>
     <t xml:space="preserve">Harald Østberg Amundsen</t>
   </si>
   <si>
     <t xml:space="preserve">0.625561180597453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592925248811894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.658197112383012</t>
-  </si>
-  <si>
     <t xml:space="preserve">Erik Valnes</t>
   </si>
   <si>
     <t xml:space="preserve">0.539046272989469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51144329532847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.566649250650469</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pål Golberg</t>
   </si>
   <si>
     <t xml:space="preserve">0.521521402846531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471989092025452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.571053713667609</t>
-  </si>
-  <si>
     <t xml:space="preserve">Martin Løwstrøm Nyenget</t>
   </si>
   <si>
     <t xml:space="preserve">0.479925953257268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.448765156837513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.511086749677023</t>
-  </si>
-  <si>
     <t xml:space="preserve">Federico Pellegrino</t>
   </si>
   <si>
@@ -104,12 +68,6 @@
     <t xml:space="preserve">0.404314699076734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363258261575977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.445371136577491</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calle Halfvarsson</t>
   </si>
   <si>
@@ -119,24 +77,12 @@
     <t xml:space="preserve">0.341822375642574</t>
   </si>
   <si>
-    <t xml:space="preserve">0.320187432453656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.363457318831492</t>
-  </si>
-  <si>
     <t xml:space="preserve">Håvard Solås Taugbøl</t>
   </si>
   <si>
     <t xml:space="preserve">0.319825544653543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295909139603935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343741949703151</t>
-  </si>
-  <si>
     <t xml:space="preserve">Iivo Niskanen</t>
   </si>
   <si>
@@ -146,24 +92,12 @@
     <t xml:space="preserve">0.319504409472048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.295384415880296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.343624403063799</t>
-  </si>
-  <si>
     <t xml:space="preserve">Simen Hegstad Krüger</t>
   </si>
   <si>
     <t xml:space="preserve">0.313406609797827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.290607190257944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.33620602933771</t>
-  </si>
-  <si>
     <t xml:space="preserve">Michal Novak</t>
   </si>
   <si>
@@ -173,24 +107,12 @@
     <t xml:space="preserve">0.300795461701481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.279907405677101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.321683517725861</t>
-  </si>
-  <si>
     <t xml:space="preserve">Didrik Tønseth</t>
   </si>
   <si>
     <t xml:space="preserve">0.294810804547993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.272400987472065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31722062162392</t>
-  </si>
-  <si>
     <t xml:space="preserve">Friedrich Moch</t>
   </si>
   <si>
@@ -200,12 +122,6 @@
     <t xml:space="preserve">0.292441948304585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.270691935921084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314191960688085</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ben Ogden</t>
   </si>
   <si>
@@ -215,12 +131,6 @@
     <t xml:space="preserve">0.291337882314572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.269221818865395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.313453945763749</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lucas Chanavat</t>
   </si>
   <si>
@@ -230,12 +140,6 @@
     <t xml:space="preserve">0.286212613571558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251635393582287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32078983356083</t>
-  </si>
-  <si>
     <t xml:space="preserve">Antoine Cyr</t>
   </si>
   <si>
@@ -245,48 +149,24 @@
     <t xml:space="preserve">0.284398550618107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265696029425323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303101071810891</t>
-  </si>
-  <si>
     <t xml:space="preserve">Even Northug</t>
   </si>
   <si>
     <t xml:space="preserve">0.283442474961993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.26016041071787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306724539206115</t>
-  </si>
-  <si>
     <t xml:space="preserve">William Poromaa</t>
   </si>
   <si>
     <t xml:space="preserve">0.282190548123479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261959434170143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.302421662076814</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hugo Lapalus</t>
   </si>
   <si>
     <t xml:space="preserve">0.280517466041161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257506305788865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.303528626293457</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mika Vermeulen</t>
   </si>
   <si>
@@ -296,156 +176,78 @@
     <t xml:space="preserve">0.278955533309507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258007125905859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.299903940713155</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jan Thomas Jenssen</t>
   </si>
   <si>
     <t xml:space="preserve">0.278139331030497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.259348425642085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.296930236418909</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gus Schumacher</t>
   </si>
   <si>
     <t xml:space="preserve">0.276069347314289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25700481874471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.295133875883868</t>
-  </si>
-  <si>
     <t xml:space="preserve">Richard Jouve</t>
   </si>
   <si>
     <t xml:space="preserve">0.276016950299244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.251914434004767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300119466593721</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lauri Vuorinen</t>
   </si>
   <si>
     <t xml:space="preserve">0.275284668279073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257739666606365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.292829669951782</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jens Burman</t>
   </si>
   <si>
     <t xml:space="preserve">0.266469285918133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.244707067940622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.288231503895644</t>
-  </si>
-  <si>
     <t xml:space="preserve">Johan Häggström</t>
   </si>
   <si>
     <t xml:space="preserve">0.255497852241805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23751233183149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273483372652121</t>
-  </si>
-  <si>
     <t xml:space="preserve">Perttu Hyvärinen</t>
   </si>
   <si>
     <t xml:space="preserve">0.255402740531479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237631935871105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273173545191852</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mattis Stenshagen</t>
   </si>
   <si>
     <t xml:space="preserve">0.253285500458432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.234301868723402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.272269132193462</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jules Chappaz</t>
   </si>
   <si>
     <t xml:space="preserve">0.241854796863245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.221464323391316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.262245270335174</t>
-  </si>
-  <si>
     <t xml:space="preserve">Edvin Anger</t>
   </si>
   <si>
     <t xml:space="preserve">0.239462719176746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217128913784275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.261796524569218</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ristomatti Hakola</t>
   </si>
   <si>
     <t xml:space="preserve">0.2359041909572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214925589614707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.256882792299694</t>
-  </si>
-  <si>
     <t xml:space="preserve">Joni Mäki</t>
   </si>
   <si>
     <t xml:space="preserve">0.234552101550118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216829731640231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.252274471460006</t>
-  </si>
-  <si>
     <t xml:space="preserve">Valerio Grond</t>
   </si>
   <si>
@@ -455,12 +257,6 @@
     <t xml:space="preserve">0.231809706467781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.213123883947652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25049552898791</t>
-  </si>
-  <si>
     <t xml:space="preserve">Andrew Musgrave</t>
   </si>
   <si>
@@ -470,240 +266,120 @@
     <t xml:space="preserve">0.205190741586641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185525256818985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.224856226354297</t>
-  </si>
-  <si>
     <t xml:space="preserve">Henrik Dønnestad</t>
   </si>
   <si>
     <t xml:space="preserve">0.204350220889415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184476001910395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.224224439868434</t>
-  </si>
-  <si>
     <t xml:space="preserve">Theo Schely</t>
   </si>
   <si>
     <t xml:space="preserve">0.202907024352357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184865176134176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.220948872570538</t>
-  </si>
-  <si>
     <t xml:space="preserve">James Clinton Schoonmaker</t>
   </si>
   <si>
     <t xml:space="preserve">0.19323841473924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174416622678055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.212060206800424</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jules Lapierre</t>
   </si>
   <si>
     <t xml:space="preserve">0.193167346777469</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17527665210819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.211058041446749</t>
-  </si>
-  <si>
     <t xml:space="preserve">Beda Klee</t>
   </si>
   <si>
     <t xml:space="preserve">0.188456484971005</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171284690446269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.205628279495741</t>
-  </si>
-  <si>
     <t xml:space="preserve">Francesco De Fabiani</t>
   </si>
   <si>
     <t xml:space="preserve">0.168325050279199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144489424781549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.19216067577685</t>
-  </si>
-  <si>
     <t xml:space="preserve">Elia Barp</t>
   </si>
   <si>
     <t xml:space="preserve">0.162117515047594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143938443492115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.180296586603073</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cyril Fähndrich</t>
   </si>
   <si>
     <t xml:space="preserve">0.159360438184191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14250813159549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176212744772892</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zanden McMullen</t>
   </si>
   <si>
     <t xml:space="preserve">0.15596582636167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138182663442337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173748989281002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Leo Johansson</t>
   </si>
   <si>
     <t xml:space="preserve">0.15340033241952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135010505829065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171790159009975</t>
-  </si>
-  <si>
     <t xml:space="preserve">Davide Graz</t>
   </si>
   <si>
     <t xml:space="preserve">0.153131755745083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137327166908884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168936344581281</t>
-  </si>
-  <si>
     <t xml:space="preserve">Renaud Jay</t>
   </si>
   <si>
     <t xml:space="preserve">0.14970767207047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127985966498755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171429377642185</t>
-  </si>
-  <si>
     <t xml:space="preserve">Marcus Grate</t>
   </si>
   <si>
     <t xml:space="preserve">0.148797626887153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13203949442847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165555759345837</t>
-  </si>
-  <si>
     <t xml:space="preserve">Florian Notz</t>
   </si>
   <si>
     <t xml:space="preserve">0.146818130589547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.122082984739751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171553276439344</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oskar Svensson</t>
   </si>
   <si>
     <t xml:space="preserve">0.139477934553622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.123538295229624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155417573877619</t>
-  </si>
-  <si>
     <t xml:space="preserve">Janik Riebli</t>
   </si>
   <si>
     <t xml:space="preserve">0.139182345676536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.122407736774494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155956954578578</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remi Lindholm</t>
   </si>
   <si>
     <t xml:space="preserve">0.13566524226066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118766838431065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152563646090254</t>
-  </si>
-  <si>
     <t xml:space="preserve">Simone Dapra</t>
   </si>
   <si>
     <t xml:space="preserve">0.133594577316161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116899038072812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15029011655951</t>
-  </si>
-  <si>
     <t xml:space="preserve">Emil Danielsson</t>
   </si>
   <si>
     <t xml:space="preserve">0.125278408033672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10858639916903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141970416898314</t>
-  </si>
-  <si>
     <t xml:space="preserve">Naoto Baba</t>
   </si>
   <si>
@@ -713,156 +389,78 @@
     <t xml:space="preserve">0.12419024571844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107890903709522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140489587727357</t>
-  </si>
-  <si>
     <t xml:space="preserve">Niilo Moilanen</t>
   </si>
   <si>
     <t xml:space="preserve">0.123798656442481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107130033894603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140467278990358</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ansgar Evensen</t>
   </si>
   <si>
     <t xml:space="preserve">0.122861682265002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107010931530274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13871243299973</t>
-  </si>
-  <si>
     <t xml:space="preserve">Matz William Jenssen</t>
   </si>
   <si>
     <t xml:space="preserve">0.119958842693257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104258580727736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135659104658778</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arsi Ruuskanen</t>
   </si>
   <si>
     <t xml:space="preserve">0.117259505756462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102461284348112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132057727164812</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maurice Manificat</t>
   </si>
   <si>
     <t xml:space="preserve">0.116848647645495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0931256911374564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140571604153534</t>
-  </si>
-  <si>
     <t xml:space="preserve">Markus Vuorela</t>
   </si>
   <si>
     <t xml:space="preserve">0.112675104545272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0969469885024474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128403220588097</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dietmar Nöckler</t>
   </si>
   <si>
     <t xml:space="preserve">0.112165014108413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0974767854291188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126853242787707</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jonas Baumann</t>
   </si>
   <si>
     <t xml:space="preserve">0.111366020695192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0926558287323807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130076212658004</t>
-  </si>
-  <si>
     <t xml:space="preserve">Michael Hellweger</t>
   </si>
   <si>
     <t xml:space="preserve">0.111024792011245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0955480903711354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126501493651355</t>
-  </si>
-  <si>
     <t xml:space="preserve">Scott Patterson</t>
   </si>
   <si>
     <t xml:space="preserve">0.109994551387952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0873095856042379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132679517171667</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remi Bourdin</t>
   </si>
   <si>
     <t xml:space="preserve">0.106526311771289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0907936545395455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122258969003033</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gustaf Berglund</t>
   </si>
   <si>
     <t xml:space="preserve">0.106134006408726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0910800606450968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121187952172356</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thomas Hjalmar Westgård</t>
   </si>
   <si>
@@ -872,276 +470,138 @@
     <t xml:space="preserve">0.105909581449442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.091026167288188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.120792995610695</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jan Stoelben</t>
   </si>
   <si>
     <t xml:space="preserve">0.105304749835245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0903696316586784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.120239868011811</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anian Sossau</t>
   </si>
   <si>
     <t xml:space="preserve">0.0984527767320281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0823390008970672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114566552566989</t>
-  </si>
-  <si>
     <t xml:space="preserve">Truls Gisselman</t>
   </si>
   <si>
     <t xml:space="preserve">0.0977958592538711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0823803307388466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113211387768896</t>
-  </si>
-  <si>
     <t xml:space="preserve">Paolo Ventura</t>
   </si>
   <si>
     <t xml:space="preserve">0.0967498735061968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0783019318374323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115197815174961</t>
-  </si>
-  <si>
     <t xml:space="preserve">Giandomenico Salvadori</t>
   </si>
   <si>
     <t xml:space="preserve">0.0957682557932365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.081234050698052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110302460888421</t>
-  </si>
-  <si>
     <t xml:space="preserve">Janosch Brugger</t>
   </si>
   <si>
     <t xml:space="preserve">0.0949912449600328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.080418792226755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109563697693311</t>
-  </si>
-  <si>
     <t xml:space="preserve">Emil Liekari</t>
   </si>
   <si>
     <t xml:space="preserve">0.0942458860588992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0781966005041826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110295171613616</t>
-  </si>
-  <si>
     <t xml:space="preserve">Benjamin Moser</t>
   </si>
   <si>
     <t xml:space="preserve">0.0938037455822268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0783059769875916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109301514176862</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ludek Seller</t>
   </si>
   <si>
     <t xml:space="preserve">0.0925086297578774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0769642184784567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108053041037298</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roman Schaad</t>
   </si>
   <si>
     <t xml:space="preserve">0.0889208925811515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0723086679389237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105533117223379</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lucas Bögl</t>
   </si>
   <si>
     <t xml:space="preserve">0.0874150870803493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0692971356144947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105533038546204</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lauri Lepistö</t>
   </si>
   <si>
     <t xml:space="preserve">0.0847856230010772</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0702840186606821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0992872273414723</t>
-  </si>
-  <si>
     <t xml:space="preserve">Andrew Young</t>
   </si>
   <si>
     <t xml:space="preserve">0.0787303320825109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0615592337704428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.095901430394579</t>
-  </si>
-  <si>
     <t xml:space="preserve">James Clugnet</t>
   </si>
   <si>
     <t xml:space="preserve">0.0724182709095689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0558644791679834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0889720626511543</t>
-  </si>
-  <si>
     <t xml:space="preserve">Candide Pralong</t>
   </si>
   <si>
     <t xml:space="preserve">0.0717266287915593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0564266590481598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0870265985349588</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zak Ketterson</t>
   </si>
   <si>
     <t xml:space="preserve">0.0701812499039901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0543284569824719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0860340428255083</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kevin Bolger</t>
   </si>
   <si>
     <t xml:space="preserve">0.0680514650198059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0522654885229167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.083837441516695</t>
-  </si>
-  <si>
     <t xml:space="preserve">Michael Föttinger</t>
   </si>
   <si>
     <t xml:space="preserve">0.0646174715342871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0494897976764626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0797451453921117</t>
-  </si>
-  <si>
     <t xml:space="preserve">Johnny Hagenbuch</t>
   </si>
   <si>
     <t xml:space="preserve">0.0601225640027787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0448400419231396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0754050860824177</t>
-  </si>
-  <si>
     <t xml:space="preserve">Xavier McKeever</t>
   </si>
   <si>
     <t xml:space="preserve">0.0578031143403108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0435373380537506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.072068890626871</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pierre Grall-Johnson</t>
   </si>
   <si>
     <t xml:space="preserve">0.0549507519202659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0405717528478417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0693297509926901</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ryo Hirose</t>
   </si>
   <si>
     <t xml:space="preserve">0.0509702233568776</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0356044757282699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0663359709854852</t>
-  </si>
-  <si>
     <t xml:space="preserve">Miha Simenc</t>
   </si>
   <si>
@@ -1151,24 +611,12 @@
     <t xml:space="preserve">0.046803093680822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0302031512483206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0634030361133233</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sasha Masson</t>
   </si>
   <si>
     <t xml:space="preserve">0.0456235723154866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0307934443637264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0604537002672468</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maciej Starega</t>
   </si>
   <si>
@@ -1178,48 +626,24 @@
     <t xml:space="preserve">0.0440190167754482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00592702203358701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0821110115173093</t>
-  </si>
-  <si>
     <t xml:space="preserve">Olivier Leveille</t>
   </si>
   <si>
     <t xml:space="preserve">0.0419923666365187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0260470406867512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0579376925862862</t>
-  </si>
-  <si>
     <t xml:space="preserve">Luke Jager</t>
   </si>
   <si>
     <t xml:space="preserve">0.0418967842038792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0278570746967521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0559364937110062</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peter Wolter</t>
   </si>
   <si>
     <t xml:space="preserve">0.0393694300396688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0251996120465542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0535392480327834</t>
-  </si>
-  <si>
     <t xml:space="preserve">Martin Himma</t>
   </si>
   <si>
@@ -1229,84 +653,42 @@
     <t xml:space="preserve">0.0387956006278168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.02293579707631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0546554041793236</t>
-  </si>
-  <si>
     <t xml:space="preserve">Michael Earnhart</t>
   </si>
   <si>
     <t xml:space="preserve">0.038388479963402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0239030182921429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0528739416346611</t>
-  </si>
-  <si>
     <t xml:space="preserve">Erwan Käser</t>
   </si>
   <si>
     <t xml:space="preserve">0.0380805718058849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0216180893809545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0545430542308152</t>
-  </si>
-  <si>
     <t xml:space="preserve">Adam Fellner</t>
   </si>
   <si>
     <t xml:space="preserve">0.0326330928150912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0173065073958442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0479596782343382</t>
-  </si>
-  <si>
     <t xml:space="preserve">Leo Grandbois</t>
   </si>
   <si>
     <t xml:space="preserve">0.0311073946828331</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0165289977462107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0456857916194555</t>
-  </si>
-  <si>
     <t xml:space="preserve">Miha Licef</t>
   </si>
   <si>
     <t xml:space="preserve">0.028915083999321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0131626078753078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0446675601233341</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kamil Bury</t>
   </si>
   <si>
     <t xml:space="preserve">0.0287250256418518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0119526080316727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0454974432520309</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nikita Gridin</t>
   </si>
   <si>
@@ -1316,36 +698,18 @@
     <t xml:space="preserve">0.0280111491200252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0131176505493513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0429046476906992</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dominik Bury</t>
   </si>
   <si>
     <t xml:space="preserve">0.027344698538695</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00875133027373267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0459380668036573</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anze Gros</t>
   </si>
   <si>
     <t xml:space="preserve">0.0265996141522917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0109770609933573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0422221673112261</t>
-  </si>
-  <si>
     <t xml:space="preserve">Imanol Rojo</t>
   </si>
   <si>
@@ -1355,96 +719,48 @@
     <t xml:space="preserve">0.0264525810885925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00661617871697241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0462889834602125</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fedor Karpov</t>
   </si>
   <si>
     <t xml:space="preserve">0.0263324129598952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00878324476849655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0438815811512938</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alvar Johannes Alev</t>
   </si>
   <si>
     <t xml:space="preserve">0.0259788120463809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00933453501329103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0426230890794707</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vili Crv</t>
   </si>
   <si>
     <t xml:space="preserve">0.0234652293198411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00623164926163938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0406988093780428</t>
-  </si>
-  <si>
     <t xml:space="preserve">Konstantin Bortsov</t>
   </si>
   <si>
     <t xml:space="preserve">0.0223331827229086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00570529044027109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0389610750055462</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vladislav Kovalyov</t>
   </si>
   <si>
     <t xml:space="preserve">0.022185133926952</t>
   </si>
   <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.050549802501925</t>
-  </si>
-  <si>
     <t xml:space="preserve">Olzhas Klimin</t>
   </si>
   <si>
     <t xml:space="preserve">0.0210003476843643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00319088362878658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0388098117399421</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nail Bashmakov</t>
   </si>
   <si>
     <t xml:space="preserve">0.0194653507873036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00166793314685897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0372627684277483</t>
-  </si>
-  <si>
     <t xml:space="preserve">Simeon Deyanov</t>
   </si>
   <si>
@@ -1454,21 +770,12 @@
     <t xml:space="preserve">0.0193017029441194</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00125386806473882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0373495378235</t>
-  </si>
-  <si>
     <t xml:space="preserve">Julien Locke</t>
   </si>
   <si>
     <t xml:space="preserve">0.0192368538420551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0499131718544788</t>
-  </si>
-  <si>
     <t xml:space="preserve">Seve De Campo</t>
   </si>
   <si>
@@ -1476,9 +783,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.0179540790217437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0523822967963188</t>
   </si>
 </sst>
 </file>
@@ -1820,2331 +1124,1629 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>0.740923076923077</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
         <v>0.748615384615385</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
         <v>0.639076923076923</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
         <v>0.640615384615385</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
         <v>0.458769230769231</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>0.418769230769231</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>0.377538461538462</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>0.327076923076923</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>0.266769230769231</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>0.313230769230769</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
         <v>0.201846153846154</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>0.268615384615385</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
         <v>0.430153846153846</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C15" t="n">
         <v>0.241846153846154</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C16" t="n">
         <v>0.259692307692308</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C17" t="n">
         <v>0.394461538461538</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
         <v>0.264307692307692</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F18" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
         <v>0.314461538461538</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" t="s">
-        <v>85</v>
-      </c>
-      <c r="F19" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C20" t="n">
         <v>0.382153846153846</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" t="s">
-        <v>89</v>
-      </c>
-      <c r="F20" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C21" t="n">
         <v>0.370153846153846</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
         <v>0.245230769230769</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
-      </c>
-      <c r="E22" t="s">
-        <v>98</v>
-      </c>
-      <c r="F22" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C23" t="n">
         <v>0.332</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
-      </c>
-      <c r="E23" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C24" t="n">
         <v>0.292923076923077</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" t="s">
-        <v>106</v>
-      </c>
-      <c r="F24" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C25" t="n">
         <v>0.324923076923077</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" t="s">
-        <v>110</v>
-      </c>
-      <c r="F25" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C26" t="n">
         <v>0.322153846153846</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
-      </c>
-      <c r="E26" t="s">
-        <v>114</v>
-      </c>
-      <c r="F26" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C27" t="n">
         <v>0.361230769230769</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
-      </c>
-      <c r="E27" t="s">
-        <v>118</v>
-      </c>
-      <c r="F27" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C28" t="n">
         <v>0.228</v>
       </c>
       <c r="D28" t="s">
-        <v>121</v>
-      </c>
-      <c r="E28" t="s">
-        <v>122</v>
-      </c>
-      <c r="F28" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
         <v>0.190461538461538</v>
       </c>
       <c r="D29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E29" t="s">
-        <v>126</v>
-      </c>
-      <c r="F29" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C30" t="n">
         <v>0.273230769230769</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
-      </c>
-      <c r="E30" t="s">
-        <v>130</v>
-      </c>
-      <c r="F30" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C31" t="n">
         <v>0.328307692307692</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
-      </c>
-      <c r="E31" t="s">
-        <v>134</v>
-      </c>
-      <c r="F31" t="s">
-        <v>135</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C32" t="n">
         <v>0.112</v>
       </c>
       <c r="D32" t="s">
-        <v>137</v>
-      </c>
-      <c r="E32" t="s">
-        <v>138</v>
-      </c>
-      <c r="F32" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C33" t="n">
         <v>0.225846153846154</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" t="s">
-        <v>142</v>
-      </c>
-      <c r="F33" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C34" t="n">
         <v>0.256923076923077</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
-      </c>
-      <c r="E34" t="s">
-        <v>147</v>
-      </c>
-      <c r="F34" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>149</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C35" t="n">
         <v>0.260307692307692</v>
       </c>
       <c r="D35" t="s">
-        <v>151</v>
-      </c>
-      <c r="E35" t="s">
-        <v>152</v>
-      </c>
-      <c r="F35" t="s">
-        <v>153</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
         <v>0.171076923076923</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
-      </c>
-      <c r="E36" t="s">
-        <v>156</v>
-      </c>
-      <c r="F36" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C37" t="n">
         <v>0.228</v>
       </c>
       <c r="D37" t="s">
-        <v>159</v>
-      </c>
-      <c r="E37" t="s">
-        <v>160</v>
-      </c>
-      <c r="F37" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C38" t="n">
         <v>0.208307692307692</v>
       </c>
       <c r="D38" t="s">
-        <v>163</v>
-      </c>
-      <c r="E38" t="s">
-        <v>164</v>
-      </c>
-      <c r="F38" t="s">
-        <v>165</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C39" t="n">
         <v>0.217846153846154</v>
       </c>
       <c r="D39" t="s">
-        <v>167</v>
-      </c>
-      <c r="E39" t="s">
-        <v>168</v>
-      </c>
-      <c r="F39" t="s">
-        <v>169</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>170</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C40" t="n">
         <v>0.321538461538462</v>
       </c>
       <c r="D40" t="s">
-        <v>171</v>
-      </c>
-      <c r="E40" t="s">
-        <v>172</v>
-      </c>
-      <c r="F40" t="s">
-        <v>173</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C41" t="n">
         <v>0.0606153846153846</v>
       </c>
       <c r="D41" t="s">
-        <v>175</v>
-      </c>
-      <c r="E41" t="s">
-        <v>176</v>
-      </c>
-      <c r="F41" t="s">
-        <v>177</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C42" t="n">
         <v>0.276307692307692</v>
       </c>
       <c r="D42" t="s">
-        <v>179</v>
-      </c>
-      <c r="E42" t="s">
-        <v>180</v>
-      </c>
-      <c r="F42" t="s">
-        <v>181</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="B43" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C43" t="n">
         <v>0.170461538461538</v>
       </c>
       <c r="D43" t="s">
-        <v>183</v>
-      </c>
-      <c r="E43" t="s">
-        <v>184</v>
-      </c>
-      <c r="F43" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="B44" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C44" t="n">
         <v>0.185230769230769</v>
       </c>
       <c r="D44" t="s">
-        <v>187</v>
-      </c>
-      <c r="E44" t="s">
-        <v>188</v>
-      </c>
-      <c r="F44" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C45" t="n">
         <v>0.152</v>
       </c>
       <c r="D45" t="s">
-        <v>191</v>
-      </c>
-      <c r="E45" t="s">
-        <v>192</v>
-      </c>
-      <c r="F45" t="s">
-        <v>193</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C46" t="n">
         <v>0.143384615384615</v>
       </c>
       <c r="D46" t="s">
-        <v>195</v>
-      </c>
-      <c r="E46" t="s">
-        <v>196</v>
-      </c>
-      <c r="F46" t="s">
-        <v>197</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>198</v>
+        <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C47" t="n">
         <v>0.151076923076923</v>
       </c>
       <c r="D47" t="s">
-        <v>199</v>
-      </c>
-      <c r="E47" t="s">
-        <v>200</v>
-      </c>
-      <c r="F47" t="s">
-        <v>201</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C48" t="n">
         <v>0.119384615384615</v>
       </c>
       <c r="D48" t="s">
-        <v>203</v>
-      </c>
-      <c r="E48" t="s">
-        <v>204</v>
-      </c>
-      <c r="F48" t="s">
-        <v>205</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>206</v>
+        <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C49" t="n">
         <v>0.124923076923077</v>
       </c>
       <c r="D49" t="s">
-        <v>207</v>
-      </c>
-      <c r="E49" t="s">
-        <v>208</v>
-      </c>
-      <c r="F49" t="s">
-        <v>209</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>210</v>
+        <v>112</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C50" t="n">
         <v>0.111384615384615</v>
       </c>
       <c r="D50" t="s">
-        <v>211</v>
-      </c>
-      <c r="E50" t="s">
-        <v>212</v>
-      </c>
-      <c r="F50" t="s">
-        <v>213</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>214</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C51" t="n">
         <v>0.155692307692308</v>
       </c>
       <c r="D51" t="s">
-        <v>215</v>
-      </c>
-      <c r="E51" t="s">
-        <v>216</v>
-      </c>
-      <c r="F51" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>218</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C52" t="n">
         <v>0.141538461538462</v>
       </c>
       <c r="D52" t="s">
-        <v>219</v>
-      </c>
-      <c r="E52" t="s">
-        <v>220</v>
-      </c>
-      <c r="F52" t="s">
-        <v>221</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>222</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C53" t="n">
         <v>0.157846153846154</v>
       </c>
       <c r="D53" t="s">
-        <v>223</v>
-      </c>
-      <c r="E53" t="s">
-        <v>224</v>
-      </c>
-      <c r="F53" t="s">
-        <v>225</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>226</v>
+        <v>120</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C54" t="n">
         <v>0.124923076923077</v>
       </c>
       <c r="D54" t="s">
-        <v>227</v>
-      </c>
-      <c r="E54" t="s">
-        <v>228</v>
-      </c>
-      <c r="F54" t="s">
-        <v>229</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>230</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>231</v>
+        <v>123</v>
       </c>
       <c r="C55" t="n">
         <v>0.110769230769231</v>
       </c>
       <c r="D55" t="s">
-        <v>232</v>
-      </c>
-      <c r="E55" t="s">
-        <v>233</v>
-      </c>
-      <c r="F55" t="s">
-        <v>234</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>235</v>
+        <v>125</v>
       </c>
       <c r="B56" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C56" t="n">
         <v>0.103076923076923</v>
       </c>
       <c r="D56" t="s">
-        <v>236</v>
-      </c>
-      <c r="E56" t="s">
-        <v>237</v>
-      </c>
-      <c r="F56" t="s">
-        <v>238</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>239</v>
+        <v>127</v>
       </c>
       <c r="B57" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C57" t="n">
         <v>0.139076923076923</v>
       </c>
       <c r="D57" t="s">
-        <v>240</v>
-      </c>
-      <c r="E57" t="s">
-        <v>241</v>
-      </c>
-      <c r="F57" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>243</v>
+        <v>129</v>
       </c>
       <c r="B58" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C58" t="n">
         <v>0.115076923076923</v>
       </c>
       <c r="D58" t="s">
-        <v>244</v>
-      </c>
-      <c r="E58" t="s">
-        <v>245</v>
-      </c>
-      <c r="F58" t="s">
-        <v>246</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>247</v>
+        <v>131</v>
       </c>
       <c r="B59" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C59" t="n">
         <v>0.117230769230769</v>
       </c>
       <c r="D59" t="s">
-        <v>248</v>
-      </c>
-      <c r="E59" t="s">
-        <v>249</v>
-      </c>
-      <c r="F59" t="s">
-        <v>250</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>251</v>
+        <v>133</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C60" t="n">
         <v>0.0630769230769231</v>
       </c>
       <c r="D60" t="s">
-        <v>252</v>
-      </c>
-      <c r="E60" t="s">
-        <v>253</v>
-      </c>
-      <c r="F60" t="s">
-        <v>254</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>255</v>
+        <v>135</v>
       </c>
       <c r="B61" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C61" t="n">
         <v>0.136307692307692</v>
       </c>
       <c r="D61" t="s">
-        <v>256</v>
-      </c>
-      <c r="E61" t="s">
-        <v>257</v>
-      </c>
-      <c r="F61" t="s">
-        <v>258</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>259</v>
+        <v>137</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C62" t="n">
         <v>0.0458461538461538</v>
       </c>
       <c r="D62" t="s">
-        <v>260</v>
-      </c>
-      <c r="E62" t="s">
-        <v>261</v>
-      </c>
-      <c r="F62" t="s">
-        <v>262</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>263</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C63" t="n">
         <v>0.0846153846153846</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
-      </c>
-      <c r="E63" t="s">
-        <v>265</v>
-      </c>
-      <c r="F63" t="s">
-        <v>266</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>267</v>
+        <v>141</v>
       </c>
       <c r="B64" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C64" t="n">
         <v>0.0972307692307692</v>
       </c>
       <c r="D64" t="s">
-        <v>268</v>
-      </c>
-      <c r="E64" t="s">
-        <v>269</v>
-      </c>
-      <c r="F64" t="s">
-        <v>270</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>271</v>
+        <v>143</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C65" t="n">
         <v>0.173230769230769</v>
       </c>
       <c r="D65" t="s">
-        <v>272</v>
-      </c>
-      <c r="E65" t="s">
-        <v>273</v>
-      </c>
-      <c r="F65" t="s">
-        <v>274</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>275</v>
+        <v>145</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C66" t="n">
         <v>0.072</v>
       </c>
       <c r="D66" t="s">
-        <v>276</v>
-      </c>
-      <c r="E66" t="s">
-        <v>277</v>
-      </c>
-      <c r="F66" t="s">
-        <v>278</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>279</v>
+        <v>147</v>
       </c>
       <c r="B67" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C67" t="n">
         <v>0.142153846153846</v>
       </c>
       <c r="D67" t="s">
-        <v>280</v>
-      </c>
-      <c r="E67" t="s">
-        <v>281</v>
-      </c>
-      <c r="F67" t="s">
-        <v>282</v>
+        <v>148</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>283</v>
+        <v>149</v>
       </c>
       <c r="B68" t="s">
-        <v>284</v>
+        <v>150</v>
       </c>
       <c r="C68" t="n">
         <v>0.115692307692308</v>
       </c>
       <c r="D68" t="s">
-        <v>285</v>
-      </c>
-      <c r="E68" t="s">
-        <v>286</v>
-      </c>
-      <c r="F68" t="s">
-        <v>287</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="B69" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C69" t="n">
         <v>0.101538461538462</v>
       </c>
       <c r="D69" t="s">
-        <v>289</v>
-      </c>
-      <c r="E69" t="s">
-        <v>290</v>
-      </c>
-      <c r="F69" t="s">
-        <v>291</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>292</v>
+        <v>154</v>
       </c>
       <c r="B70" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C70" t="n">
         <v>0.114769230769231</v>
       </c>
       <c r="D70" t="s">
-        <v>293</v>
-      </c>
-      <c r="E70" t="s">
-        <v>294</v>
-      </c>
-      <c r="F70" t="s">
-        <v>295</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>296</v>
+        <v>156</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C71" t="n">
         <v>0.0584615384615385</v>
       </c>
       <c r="D71" t="s">
-        <v>297</v>
-      </c>
-      <c r="E71" t="s">
-        <v>298</v>
-      </c>
-      <c r="F71" t="s">
-        <v>299</v>
+        <v>157</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>300</v>
+        <v>158</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C72" t="n">
         <v>0.110461538461538</v>
       </c>
       <c r="D72" t="s">
-        <v>301</v>
-      </c>
-      <c r="E72" t="s">
-        <v>302</v>
-      </c>
-      <c r="F72" t="s">
-        <v>303</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>304</v>
+        <v>160</v>
       </c>
       <c r="B73" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C73" t="n">
         <v>0.0636923076923077</v>
       </c>
       <c r="D73" t="s">
-        <v>305</v>
-      </c>
-      <c r="E73" t="s">
-        <v>306</v>
-      </c>
-      <c r="F73" t="s">
-        <v>307</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>308</v>
+        <v>162</v>
       </c>
       <c r="B74" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C74" t="n">
         <v>0.0972307692307692</v>
       </c>
       <c r="D74" t="s">
-        <v>309</v>
-      </c>
-      <c r="E74" t="s">
-        <v>310</v>
-      </c>
-      <c r="F74" t="s">
-        <v>311</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>312</v>
+        <v>164</v>
       </c>
       <c r="B75" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C75" t="n">
         <v>0.0723076923076923</v>
       </c>
       <c r="D75" t="s">
-        <v>313</v>
-      </c>
-      <c r="E75" t="s">
-        <v>314</v>
-      </c>
-      <c r="F75" t="s">
-        <v>315</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>316</v>
+        <v>166</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C76" t="n">
         <v>0.0929230769230769</v>
       </c>
       <c r="D76" t="s">
-        <v>317</v>
-      </c>
-      <c r="E76" t="s">
-        <v>318</v>
-      </c>
-      <c r="F76" t="s">
-        <v>319</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>320</v>
+        <v>168</v>
       </c>
       <c r="B77" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C77" t="n">
         <v>0.0526153846153846</v>
       </c>
       <c r="D77" t="s">
-        <v>321</v>
-      </c>
-      <c r="E77" t="s">
-        <v>322</v>
-      </c>
-      <c r="F77" t="s">
-        <v>323</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>324</v>
+        <v>170</v>
       </c>
       <c r="B78" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C78" t="n">
         <v>0.0535384615384615</v>
       </c>
       <c r="D78" t="s">
-        <v>325</v>
-      </c>
-      <c r="E78" t="s">
-        <v>326</v>
-      </c>
-      <c r="F78" t="s">
-        <v>327</v>
+        <v>171</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>328</v>
+        <v>172</v>
       </c>
       <c r="B79" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C79" t="n">
         <v>0.110769230769231</v>
       </c>
       <c r="D79" t="s">
-        <v>329</v>
-      </c>
-      <c r="E79" t="s">
-        <v>330</v>
-      </c>
-      <c r="F79" t="s">
-        <v>331</v>
+        <v>173</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>332</v>
+        <v>174</v>
       </c>
       <c r="B80" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C80" t="n">
         <v>0.0812307692307692</v>
       </c>
       <c r="D80" t="s">
-        <v>333</v>
-      </c>
-      <c r="E80" t="s">
-        <v>334</v>
-      </c>
-      <c r="F80" t="s">
-        <v>335</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>336</v>
+        <v>176</v>
       </c>
       <c r="B81" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C81" t="n">
         <v>0.0806153846153846</v>
       </c>
       <c r="D81" t="s">
-        <v>337</v>
-      </c>
-      <c r="E81" t="s">
-        <v>338</v>
-      </c>
-      <c r="F81" t="s">
-        <v>339</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>340</v>
+        <v>178</v>
       </c>
       <c r="B82" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C82" t="n">
         <v>0.0963076923076923</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
-      </c>
-      <c r="E82" t="s">
-        <v>342</v>
-      </c>
-      <c r="F82" t="s">
-        <v>343</v>
+        <v>179</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>344</v>
+        <v>180</v>
       </c>
       <c r="B83" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C83" t="n">
         <v>0.0190769230769231</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
-      </c>
-      <c r="E83" t="s">
-        <v>346</v>
-      </c>
-      <c r="F83" t="s">
-        <v>347</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>348</v>
+        <v>182</v>
       </c>
       <c r="B84" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C84" t="n">
         <v>0.107384615384615</v>
       </c>
       <c r="D84" t="s">
-        <v>349</v>
-      </c>
-      <c r="E84" t="s">
-        <v>350</v>
-      </c>
-      <c r="F84" t="s">
-        <v>351</v>
+        <v>183</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>352</v>
+        <v>184</v>
       </c>
       <c r="B85" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C85" t="n">
         <v>0.0864615384615385</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
-      </c>
-      <c r="E85" t="s">
-        <v>354</v>
-      </c>
-      <c r="F85" t="s">
-        <v>355</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>356</v>
+        <v>186</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C86" t="n">
         <v>0.0664615384615385</v>
       </c>
       <c r="D86" t="s">
-        <v>357</v>
-      </c>
-      <c r="E86" t="s">
-        <v>358</v>
-      </c>
-      <c r="F86" t="s">
-        <v>359</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="B87" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C87" t="n">
         <v>0.0547692307692308</v>
       </c>
       <c r="D87" t="s">
-        <v>361</v>
-      </c>
-      <c r="E87" t="s">
-        <v>362</v>
-      </c>
-      <c r="F87" t="s">
-        <v>363</v>
+        <v>189</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>364</v>
+        <v>190</v>
       </c>
       <c r="B88" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C88" t="n">
         <v>0.104</v>
       </c>
       <c r="D88" t="s">
-        <v>365</v>
-      </c>
-      <c r="E88" t="s">
-        <v>366</v>
-      </c>
-      <c r="F88" t="s">
-        <v>367</v>
+        <v>191</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>368</v>
+        <v>192</v>
       </c>
       <c r="B89" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C89" t="n">
         <v>0.0529230769230769</v>
       </c>
       <c r="D89" t="s">
-        <v>369</v>
-      </c>
-      <c r="E89" t="s">
-        <v>370</v>
-      </c>
-      <c r="F89" t="s">
-        <v>371</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>372</v>
+        <v>194</v>
       </c>
       <c r="B90" t="s">
-        <v>231</v>
+        <v>123</v>
       </c>
       <c r="C90" t="n">
         <v>0.0233846153846154</v>
       </c>
       <c r="D90" t="s">
-        <v>373</v>
-      </c>
-      <c r="E90" t="s">
-        <v>374</v>
-      </c>
-      <c r="F90" t="s">
-        <v>375</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>376</v>
+        <v>196</v>
       </c>
       <c r="B91" t="s">
-        <v>377</v>
+        <v>197</v>
       </c>
       <c r="C91" t="n">
         <v>0.0603076923076923</v>
       </c>
       <c r="D91" t="s">
-        <v>378</v>
-      </c>
-      <c r="E91" t="s">
-        <v>379</v>
-      </c>
-      <c r="F91" t="s">
-        <v>380</v>
+        <v>198</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>381</v>
+        <v>199</v>
       </c>
       <c r="B92" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C92" t="n">
         <v>0.0443076923076923</v>
       </c>
       <c r="D92" t="s">
-        <v>382</v>
-      </c>
-      <c r="E92" t="s">
-        <v>383</v>
-      </c>
-      <c r="F92" t="s">
-        <v>384</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>385</v>
+        <v>201</v>
       </c>
       <c r="B93" t="s">
-        <v>386</v>
+        <v>202</v>
       </c>
       <c r="C93" t="n">
         <v>0.044</v>
       </c>
       <c r="D93" t="s">
-        <v>387</v>
-      </c>
-      <c r="E93" t="s">
-        <v>388</v>
-      </c>
-      <c r="F93" t="s">
-        <v>389</v>
+        <v>203</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>390</v>
+        <v>204</v>
       </c>
       <c r="B94" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C94" t="n">
         <v>0.0772307692307692</v>
       </c>
       <c r="D94" t="s">
-        <v>391</v>
-      </c>
-      <c r="E94" t="s">
-        <v>392</v>
-      </c>
-      <c r="F94" t="s">
-        <v>393</v>
+        <v>205</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>394</v>
+        <v>206</v>
       </c>
       <c r="B95" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C95" t="n">
         <v>0.0636923076923077</v>
       </c>
       <c r="D95" t="s">
-        <v>395</v>
-      </c>
-      <c r="E95" t="s">
-        <v>396</v>
-      </c>
-      <c r="F95" t="s">
-        <v>397</v>
+        <v>207</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>398</v>
+        <v>208</v>
       </c>
       <c r="B96" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C96" t="n">
         <v>0.00707692307692308</v>
       </c>
       <c r="D96" t="s">
-        <v>399</v>
-      </c>
-      <c r="E96" t="s">
-        <v>400</v>
-      </c>
-      <c r="F96" t="s">
-        <v>401</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>402</v>
+        <v>210</v>
       </c>
       <c r="B97" t="s">
-        <v>403</v>
+        <v>211</v>
       </c>
       <c r="C97" t="n">
         <v>0.0329230769230769</v>
       </c>
       <c r="D97" t="s">
-        <v>404</v>
-      </c>
-      <c r="E97" t="s">
-        <v>405</v>
-      </c>
-      <c r="F97" t="s">
-        <v>406</v>
+        <v>212</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>407</v>
+        <v>213</v>
       </c>
       <c r="B98" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C98" t="n">
         <v>0.0236923076923077</v>
       </c>
       <c r="D98" t="s">
-        <v>408</v>
-      </c>
-      <c r="E98" t="s">
-        <v>409</v>
-      </c>
-      <c r="F98" t="s">
-        <v>410</v>
+        <v>214</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>411</v>
+        <v>215</v>
       </c>
       <c r="B99" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C99" t="n">
         <v>0.0206153846153846</v>
       </c>
       <c r="D99" t="s">
-        <v>412</v>
-      </c>
-      <c r="E99" t="s">
-        <v>413</v>
-      </c>
-      <c r="F99" t="s">
-        <v>414</v>
+        <v>216</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>415</v>
+        <v>217</v>
       </c>
       <c r="B100" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C100" t="n">
         <v>0.0664615384615385</v>
       </c>
       <c r="D100" t="s">
-        <v>416</v>
-      </c>
-      <c r="E100" t="s">
-        <v>417</v>
-      </c>
-      <c r="F100" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="B101" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C101" t="n">
         <v>0.00676923076923077</v>
       </c>
       <c r="D101" t="s">
-        <v>420</v>
-      </c>
-      <c r="E101" t="s">
-        <v>421</v>
-      </c>
-      <c r="F101" t="s">
-        <v>422</v>
+        <v>220</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>423</v>
+        <v>221</v>
       </c>
       <c r="B102" t="s">
-        <v>377</v>
+        <v>197</v>
       </c>
       <c r="C102" t="n">
         <v>0.0135384615384615</v>
       </c>
       <c r="D102" t="s">
-        <v>424</v>
-      </c>
-      <c r="E102" t="s">
-        <v>425</v>
-      </c>
-      <c r="F102" t="s">
-        <v>426</v>
+        <v>222</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>427</v>
+        <v>223</v>
       </c>
       <c r="B103" t="s">
-        <v>386</v>
+        <v>202</v>
       </c>
       <c r="C103" t="n">
         <v>0.0421538461538462</v>
       </c>
       <c r="D103" t="s">
-        <v>428</v>
-      </c>
-      <c r="E103" t="s">
-        <v>429</v>
-      </c>
-      <c r="F103" t="s">
-        <v>430</v>
+        <v>224</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>431</v>
+        <v>225</v>
       </c>
       <c r="B104" t="s">
-        <v>432</v>
+        <v>226</v>
       </c>
       <c r="C104" t="n">
         <v>0.0135384615384615</v>
       </c>
       <c r="D104" t="s">
-        <v>433</v>
-      </c>
-      <c r="E104" t="s">
-        <v>434</v>
-      </c>
-      <c r="F104" t="s">
-        <v>435</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>436</v>
+        <v>228</v>
       </c>
       <c r="B105" t="s">
-        <v>386</v>
+        <v>202</v>
       </c>
       <c r="C105" t="n">
         <v>0.0184615384615385</v>
       </c>
       <c r="D105" t="s">
-        <v>437</v>
-      </c>
-      <c r="E105" t="s">
-        <v>438</v>
-      </c>
-      <c r="F105" t="s">
-        <v>439</v>
+        <v>229</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="B106" t="s">
-        <v>377</v>
+        <v>197</v>
       </c>
       <c r="C106" t="n">
         <v>0.00738461538461538</v>
       </c>
       <c r="D106" t="s">
-        <v>441</v>
-      </c>
-      <c r="E106" t="s">
-        <v>442</v>
-      </c>
-      <c r="F106" t="s">
-        <v>443</v>
+        <v>231</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>444</v>
+        <v>232</v>
       </c>
       <c r="B107" t="s">
-        <v>445</v>
+        <v>233</v>
       </c>
       <c r="C107" t="n">
         <v>0.0212307692307692</v>
       </c>
       <c r="D107" t="s">
-        <v>446</v>
-      </c>
-      <c r="E107" t="s">
-        <v>447</v>
-      </c>
-      <c r="F107" t="s">
-        <v>448</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>449</v>
+        <v>235</v>
       </c>
       <c r="B108" t="s">
-        <v>432</v>
+        <v>226</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="s">
-        <v>450</v>
-      </c>
-      <c r="E108" t="s">
-        <v>451</v>
-      </c>
-      <c r="F108" t="s">
-        <v>452</v>
+        <v>236</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>453</v>
+        <v>237</v>
       </c>
       <c r="B109" t="s">
-        <v>403</v>
+        <v>211</v>
       </c>
       <c r="C109" t="n">
         <v>0.0446153846153846</v>
       </c>
       <c r="D109" t="s">
-        <v>454</v>
-      </c>
-      <c r="E109" t="s">
-        <v>455</v>
-      </c>
-      <c r="F109" t="s">
-        <v>456</v>
+        <v>238</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>457</v>
+        <v>239</v>
       </c>
       <c r="B110" t="s">
-        <v>377</v>
+        <v>197</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="s">
-        <v>458</v>
-      </c>
-      <c r="E110" t="s">
-        <v>459</v>
-      </c>
-      <c r="F110" t="s">
-        <v>460</v>
+        <v>240</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>461</v>
+        <v>241</v>
       </c>
       <c r="B111" t="s">
-        <v>432</v>
+        <v>226</v>
       </c>
       <c r="C111" t="n">
         <v>0.0289230769230769</v>
       </c>
       <c r="D111" t="s">
-        <v>462</v>
-      </c>
-      <c r="E111" t="s">
-        <v>463</v>
-      </c>
-      <c r="F111" t="s">
-        <v>464</v>
+        <v>242</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>465</v>
+        <v>243</v>
       </c>
       <c r="B112" t="s">
-        <v>432</v>
+        <v>226</v>
       </c>
       <c r="C112" t="n">
         <v>0.0206153846153846</v>
       </c>
       <c r="D112" t="s">
-        <v>466</v>
-      </c>
-      <c r="E112" t="s">
-        <v>467</v>
-      </c>
-      <c r="F112" t="s">
-        <v>468</v>
+        <v>244</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>469</v>
+        <v>245</v>
       </c>
       <c r="B113" t="s">
-        <v>432</v>
+        <v>226</v>
       </c>
       <c r="C113" t="n">
         <v>0.0270769230769231</v>
       </c>
       <c r="D113" t="s">
-        <v>470</v>
-      </c>
-      <c r="E113" t="s">
-        <v>471</v>
-      </c>
-      <c r="F113" t="s">
-        <v>472</v>
+        <v>246</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>473</v>
+        <v>247</v>
       </c>
       <c r="B114" t="s">
-        <v>432</v>
+        <v>226</v>
       </c>
       <c r="C114" t="n">
         <v>0.02</v>
       </c>
       <c r="D114" t="s">
-        <v>474</v>
-      </c>
-      <c r="E114" t="s">
-        <v>475</v>
-      </c>
-      <c r="F114" t="s">
-        <v>476</v>
+        <v>248</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>477</v>
+        <v>249</v>
       </c>
       <c r="B115" t="s">
-        <v>478</v>
+        <v>250</v>
       </c>
       <c r="C115" t="n">
         <v>0.000307692307692308</v>
       </c>
       <c r="D115" t="s">
-        <v>479</v>
-      </c>
-      <c r="E115" t="s">
-        <v>480</v>
-      </c>
-      <c r="F115" t="s">
-        <v>481</v>
+        <v>251</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>482</v>
+        <v>252</v>
       </c>
       <c r="B116" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>483</v>
-      </c>
-      <c r="E116" t="s">
-        <v>467</v>
-      </c>
-      <c r="F116" t="s">
-        <v>484</v>
+        <v>253</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>485</v>
+        <v>254</v>
       </c>
       <c r="B117" t="s">
-        <v>486</v>
+        <v>255</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
       </c>
       <c r="D117" t="s">
-        <v>487</v>
-      </c>
-      <c r="E117" t="s">
-        <v>467</v>
-      </c>
-      <c r="F117" t="s">
-        <v>488</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
